--- a/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_478_Mauritania.xlsx
+++ b/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_478_Mauritania.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="R9d91b2854b6041f1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="R793bc92a915748b5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="R7df6a1eb512c4214"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="R24c3ecbea9ee4c14"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="R2b7a0b1bba004d4e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="R157fe61b0b5947a2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="R5f8aff3136064b0c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="R99a1cfa13d014139"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="Rd64ba6c5ef2b418d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="R72fcff42ed1e413e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="R8eb31e09a6264360"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="R5bec4cac3e1442c5"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -18,13 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="6">
+  <x:numFmts count="4">
     <x:numFmt numFmtId="200" formatCode="0"/>
     <x:numFmt numFmtId="201" formatCode="#,##0.00"/>
     <x:numFmt numFmtId="202" formatCode="0.0000"/>
-    <x:numFmt numFmtId="203" formatCode="#,##0"/>
-    <x:numFmt numFmtId="204" formatCode="0.00%"/>
-    <x:numFmt numFmtId="205" formatCode="0.00"/>
+    <x:numFmt numFmtId="203" formatCode="0.00"/>
   </x:numFmts>
   <x:fonts count="7">
     <x:font>
@@ -184,7 +182,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="37">
+  <x:cellXfs count="35">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <x:extLst>
@@ -244,8 +242,6 @@
     <x:xf numFmtId="200" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="201" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="202" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="203" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="204" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <x:extLst>
         <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
@@ -253,14 +249,14 @@
         </x:ext>
       </x:extLst>
     </x:xf>
-    <x:xf numFmtId="205" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="203" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
-  <x:dxfs count="3">
+  <x:dxfs count="1">
     <x:dxf>
       <x:font>
         <x:color rgb="FF9A3412"/>
@@ -268,28 +264,6 @@
       <x:fill>
         <x:patternFill patternType="solid">
           <x:bgColor rgb="FFFCEAD8"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
         </x:patternFill>
       </x:fill>
     </x:dxf>
@@ -345,56 +319,36 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ478CommercialTable" displayName="EEZ478CommercialTable" ref="A1:O12" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O12"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ478CommercialTable" displayName="EEZ478CommercialTable" ref="A1:E12" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E12"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="commercial_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ478FunctionalTable" displayName="EEZ478FunctionalTable" ref="A1:O26" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O26"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ478FunctionalTable" displayName="EEZ478FunctionalTable" ref="A1:E26" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E26"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="functional_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ478ValidationTable" displayName="EEZ478ValidationTable" ref="A1:D19" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:D19"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ478ValidationTable" displayName="EEZ478ValidationTable" ref="A1:D17" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:D17"/>
   <x:tableColumns count="4">
     <x:tableColumn id="1" name="unit_id"/>
     <x:tableColumn id="2" name="check"/>
@@ -16037,7 +15991,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ref09c2cfdd0d4330"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc98a8ea983814970"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -16047,20 +16001,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="26" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -16068,660 +16012,231 @@
         <x:v>commercial_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Anchovies</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>2493.6290108147</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>3.11</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>128.82495516931337</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>2493.6290108147</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>128.82495516931337</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$H$2:$H$230,A2,'Species'!$U$2:$U$230))</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>321241.645527103</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>3.11</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>128.82495516931337</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
-        <x:v>321241.645527103</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Cod-likes</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>77179.88106968589</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>4.425161534247805</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>2661.714890846439</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>77179.88106968589</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>2668.1147845850455</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$H$2:$H$230,A3,'Species'!$U$2:$U$230))</x:f>
-        <x:v>205924781.75454438</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>4.425161534247805</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>2661.714890846439</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>205430838.71694013</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>493943.03760424256</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>1.0024044249670072</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>0.0024044249670072113</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Crustaceans</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>7267.8845190326</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>3.084472467530927</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>121.47096104784575</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>7267.8845190326</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>148.15926066345116</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$H$2:$H$230,A4,'Species'!$U$2:$U$230))</x:f>
-        <x:v>1076804.3969272124</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>3.084472467530927</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>121.47096104784575</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>882836.9173116501</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>193967.47961556225</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>1.2197092982996427</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>0.2197092982996426</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Flatfishes</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>3643.2691632292003</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>3.3428829878654733</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>220.23330076537536</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>3643.2691632292003</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>328.03709275865907</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$H$2:$H$230,A5,'Species'!$U$2:$U$230))</x:f>
-        <x:v>1195127.4244429795</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>3.3428829878654733</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>220.23330076537536</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>802369.1933946739</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>392758.23104830564</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>1.4894981440982538</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>0.48949814409825365</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Herring-likes</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>1010067.6464611371</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>2.987836592681584</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>97.23812874785622</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>1010067.6464611371</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>112.88502165893951</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$H$2:$H$230,A6,'Species'!$U$2:$U$230))</x:f>
-        <x:v>114021508.14775951</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>2.987836592681584</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>97.23812874785622</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>98217087.85063218</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>15804420.297127336</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>1.1609131429468016</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>0.1609131429468015</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Molluscs</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>7539.9465079549</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>2.0141011499888632</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>10.330019705742984</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>7539.9465079549</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>10.697469124151723</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$H$2:$H$230,A7,'Species'!$U$2:$U$230))</x:f>
-        <x:v>80658.34496660315</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>2.0141011499888632</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>10.330019705742984</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>77887.79600742212</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>2770.548959181033</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>1.0355710278272223</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>0.035571027827222386</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="18" customHeight="1">
       <x:c r="A8" s="24" t="str">
         <x:v>Other fishes &amp; inverts</x:v>
       </x:c>
-      <x:c r="B8" s="33" t="n">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="n">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="D8" s="31" t="n">
+      <x:c r="B8" s="31" t="n">
         <x:v>266929.1401167515</x:v>
       </x:c>
+      <x:c r="C8" s="32" t="n">
+        <x:v>3.2574755442022467</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="n">
+        <x:f>IF(C8="","",(1/'Metadata'!$B$5)^(C8-1))</x:f>
+        <x:v>180.91540311080126</x:v>
+      </x:c>
       <x:c r="E8" s="31" t="n">
-        <x:v>266929.1401167515</x:v>
-      </x:c>
-      <x:c r="F8" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H8" s="32" t="n">
-        <x:f>IF(E8=0,"",I8/E8)</x:f>
-        <x:v>299.5307113298687</x:v>
-      </x:c>
-      <x:c r="I8" s="31" t="n">
-        <x:f>IF(C8=0,"",SUMIF('Species'!$H$2:$H$230,A8,'Species'!$U$2:$U$230))</x:f>
-        <x:v>79953475.21384077</x:v>
-      </x:c>
-      <x:c r="J8" s="32" t="n">
-        <x:v>3.2574755442022467</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
-        <x:f>IF(J8="","",(1/'Metadata'!$B$5)^(J8-1))</x:f>
-        <x:v>180.91540311080126</x:v>
-      </x:c>
-      <x:c r="L8" s="31" t="n">
-        <x:f>IF(E8=0,"",E8*K8)</x:f>
+        <x:f>IF(B8=0,"",B8*D8)</x:f>
         <x:v>48291592.986241646</x:v>
-      </x:c>
-      <x:c r="M8" s="31" t="n">
-        <x:f>IF(E8=0,"",I8-L8)</x:f>
-        <x:v>31661882.22759912</x:v>
-      </x:c>
-      <x:c r="N8" s="32" t="n">
-        <x:f>IF(L8=0,"",I8/L8)</x:f>
-        <x:v>1.655639631449301</x:v>
-      </x:c>
-      <x:c r="O8" s="34" t="n">
-        <x:f>IF(L8=0,"",M8/L8)</x:f>
-        <x:v>0.655639631449301</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="18" customHeight="1">
       <x:c r="A9" s="24" t="str">
         <x:v>Perch-likes</x:v>
       </x:c>
-      <x:c r="B9" s="33" t="n">
-        <x:v>103</x:v>
-      </x:c>
-      <x:c r="C9" s="33" t="n">
-        <x:v>103</x:v>
-      </x:c>
-      <x:c r="D9" s="31" t="n">
+      <x:c r="B9" s="31" t="n">
         <x:v>758540.7981321054</x:v>
       </x:c>
+      <x:c r="C9" s="32" t="n">
+        <x:v>3.658981809457478</x:v>
+      </x:c>
+      <x:c r="D9" s="32" t="n">
+        <x:f>IF(C9="","",(1/'Metadata'!$B$5)^(C9-1))</x:f>
+        <x:v>456.0178151210339</x:v>
+      </x:c>
       <x:c r="E9" s="31" t="n">
-        <x:v>758540.7981321054</x:v>
-      </x:c>
-      <x:c r="F9" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H9" s="32" t="n">
-        <x:f>IF(E9=0,"",I9/E9)</x:f>
-        <x:v>576.4536850287351</x:v>
-      </x:c>
-      <x:c r="I9" s="31" t="n">
-        <x:f>IF(C9=0,"",SUMIF('Species'!$H$2:$H$230,A9,'Species'!$U$2:$U$230))</x:f>
-        <x:v>437263638.32789</x:v>
-      </x:c>
-      <x:c r="J9" s="32" t="n">
-        <x:v>3.658981809457478</x:v>
-      </x:c>
-      <x:c r="K9" s="32" t="n">
-        <x:f>IF(J9="","",(1/'Metadata'!$B$5)^(J9-1))</x:f>
-        <x:v>456.0178151210339</x:v>
-      </x:c>
-      <x:c r="L9" s="31" t="n">
-        <x:f>IF(E9=0,"",E9*K9)</x:f>
+        <x:f>IF(B9=0,"",B9*D9)</x:f>
         <x:v>345908117.44436795</x:v>
-      </x:c>
-      <x:c r="M9" s="31" t="n">
-        <x:f>IF(E9=0,"",I9-L9)</x:f>
-        <x:v>91355520.88352203</x:v>
-      </x:c>
-      <x:c r="N9" s="32" t="n">
-        <x:f>IF(L9=0,"",I9/L9)</x:f>
-        <x:v>1.2641034317392528</x:v>
-      </x:c>
-      <x:c r="O9" s="34" t="n">
-        <x:f>IF(L9=0,"",M9/L9)</x:f>
-        <x:v>0.2641034317392527</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="18" customHeight="1">
       <x:c r="A10" s="24" t="str">
         <x:v>Scorpionfishes</x:v>
       </x:c>
-      <x:c r="B10" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C10" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D10" s="31" t="n">
+      <x:c r="B10" s="31" t="n">
         <x:v>700.947728608</x:v>
       </x:c>
+      <x:c r="C10" s="32" t="n">
+        <x:v>3.87980717237826</x:v>
+      </x:c>
+      <x:c r="D10" s="32" t="n">
+        <x:f>IF(C10="","",(1/'Metadata'!$B$5)^(C10-1))</x:f>
+        <x:v>758.2408398242363</x:v>
+      </x:c>
       <x:c r="E10" s="31" t="n">
-        <x:v>700.947728608</x:v>
-      </x:c>
-      <x:c r="F10" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G10" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H10" s="32" t="n">
-        <x:f>IF(E10=0,"",I10/E10)</x:f>
-        <x:v>799.6359193150554</x:v>
-      </x:c>
-      <x:c r="I10" s="31" t="n">
-        <x:f>IF(C10=0,"",SUMIF('Species'!$H$2:$H$230,A10,'Species'!$U$2:$U$230))</x:f>
-        <x:v>560502.981357258</x:v>
-      </x:c>
-      <x:c r="J10" s="32" t="n">
-        <x:v>3.87980717237826</x:v>
-      </x:c>
-      <x:c r="K10" s="32" t="n">
-        <x:f>IF(J10="","",(1/'Metadata'!$B$5)^(J10-1))</x:f>
-        <x:v>758.2408398242363</x:v>
-      </x:c>
-      <x:c r="L10" s="31" t="n">
-        <x:f>IF(E10=0,"",E10*K10)</x:f>
+        <x:f>IF(B10=0,"",B10*D10)</x:f>
         <x:v>531487.1944126209</x:v>
-      </x:c>
-      <x:c r="M10" s="31" t="n">
-        <x:f>IF(E10=0,"",I10-L10)</x:f>
-        <x:v>29015.78694463719</x:v>
-      </x:c>
-      <x:c r="N10" s="32" t="n">
-        <x:f>IF(L10=0,"",I10/L10)</x:f>
-        <x:v>1.054593576759087</x:v>
-      </x:c>
-      <x:c r="O10" s="34" t="n">
-        <x:f>IF(L10=0,"",M10/L10)</x:f>
-        <x:v>0.054593576759086965</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="18" customHeight="1">
       <x:c r="A11" s="24" t="str">
         <x:v>Sharks &amp; rays</x:v>
       </x:c>
-      <x:c r="B11" s="33" t="n">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="C11" s="33" t="n">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="D11" s="31" t="n">
+      <x:c r="B11" s="31" t="n">
         <x:v>15250.341856636</x:v>
       </x:c>
+      <x:c r="C11" s="32" t="n">
+        <x:v>4.051159463688035</x:v>
+      </x:c>
+      <x:c r="D11" s="32" t="n">
+        <x:f>IF(C11="","",(1/'Metadata'!$B$5)^(C11-1))</x:f>
+        <x:v>1125.017980790604</x:v>
+      </x:c>
       <x:c r="E11" s="31" t="n">
-        <x:v>15250.341856636</x:v>
-      </x:c>
-      <x:c r="F11" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G11" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H11" s="32" t="n">
-        <x:f>IF(E11=0,"",I11/E11)</x:f>
-        <x:v>1795.3776218179178</x:v>
-      </x:c>
-      <x:c r="I11" s="31" t="n">
-        <x:f>IF(C11=0,"",SUMIF('Species'!$H$2:$H$230,A11,'Species'!$U$2:$U$230))</x:f>
-        <x:v>27380122.49447739</x:v>
-      </x:c>
-      <x:c r="J11" s="32" t="n">
-        <x:v>4.051159463688035</x:v>
-      </x:c>
-      <x:c r="K11" s="32" t="n">
-        <x:f>IF(J11="","",(1/'Metadata'!$B$5)^(J11-1))</x:f>
-        <x:v>1125.017980790604</x:v>
-      </x:c>
-      <x:c r="L11" s="31" t="n">
-        <x:f>IF(E11=0,"",E11*K11)</x:f>
+        <x:f>IF(B11=0,"",B11*D11)</x:f>
         <x:v>17156908.801919065</x:v>
-      </x:c>
-      <x:c r="M11" s="31" t="n">
-        <x:f>IF(E11=0,"",I11-L11)</x:f>
-        <x:v>10223213.692558326</x:v>
-      </x:c>
-      <x:c r="N11" s="32" t="n">
-        <x:f>IF(L11=0,"",I11/L11)</x:f>
-        <x:v>1.5958657127917368</x:v>
-      </x:c>
-      <x:c r="O11" s="34" t="n">
-        <x:f>IF(L11=0,"",M11/L11)</x:f>
-        <x:v>0.5958657127917367</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="18" customHeight="1">
       <x:c r="A12" s="24" t="str">
         <x:v>Tuna &amp; billfishes</x:v>
       </x:c>
-      <x:c r="B12" s="33" t="n">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="C12" s="33" t="n">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="D12" s="31" t="n">
+      <x:c r="B12" s="31" t="n">
         <x:v>60640.4533161168</x:v>
       </x:c>
+      <x:c r="C12" s="32" t="n">
+        <x:v>4.432779774316442</x:v>
+      </x:c>
+      <x:c r="D12" s="32" t="n">
+        <x:f>IF(C12="","",(1/'Metadata'!$B$5)^(C12-1))</x:f>
+        <x:v>2708.817673606009</x:v>
+      </x:c>
       <x:c r="E12" s="31" t="n">
-        <x:v>60640.4533161168</x:v>
-      </x:c>
-      <x:c r="F12" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G12" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H12" s="32" t="n">
-        <x:f>IF(E12=0,"",I12/E12)</x:f>
-        <x:v>2718.0451611523367</x:v>
-      </x:c>
-      <x:c r="I12" s="31" t="n">
-        <x:f>IF(C12=0,"",SUMIF('Species'!$H$2:$H$230,A12,'Species'!$U$2:$U$230))</x:f>
-        <x:v>164823490.70595545</x:v>
-      </x:c>
-      <x:c r="J12" s="32" t="n">
-        <x:v>4.432779774316442</x:v>
-      </x:c>
-      <x:c r="K12" s="32" t="n">
-        <x:f>IF(J12="","",(1/'Metadata'!$B$5)^(J12-1))</x:f>
-        <x:v>2708.817673606009</x:v>
-      </x:c>
-      <x:c r="L12" s="31" t="n">
-        <x:f>IF(E12=0,"",E12*K12)</x:f>
+        <x:f>IF(B12=0,"",B12*D12)</x:f>
         <x:v>164263931.6781773</x:v>
       </x:c>
-      <x:c r="M12" s="31" t="n">
-        <x:f>IF(E12=0,"",I12-L12)</x:f>
-        <x:v>559559.0277781487</x:v>
-      </x:c>
-      <x:c r="N12" s="32" t="n">
-        <x:f>IF(L12=0,"",I12/L12)</x:f>
-        <x:v>1.003406463135647</x:v>
-      </x:c>
-      <x:c r="O12" s="34" t="n">
-        <x:f>IF(L12=0,"",M12/L12)</x:f>
-        <x:v>0.0034064631356470016</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G12">
-    <x:cfRule type="cellIs" dxfId="1" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O12">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0cdefd956b324d2e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R47bda2eb374941a3"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -16731,20 +16246,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="34" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -16752,1416 +16257,497 @@
         <x:v>functional_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Cephalopods</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>52646.8185665245</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>3.754228542085783</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>567.8433473172208</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>52646.8185665245</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>605.8906829649968</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$G$2:$G$230,A2,'Species'!$U$2:$U$230))</x:f>
-        <x:v>31898216.857205804</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>3.754228542085783</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>567.8433473172208</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>29895145.68041768</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>2003071.1767881252</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1.0670032251456865</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0.06700322514568657</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Large bathydemersals (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>54.748455558399996</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>4.35</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>2238.7211385683377</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>54.748455558399996</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>2238.7211385683377</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$G$2:$G$230,A3,'Species'!$U$2:$U$230))</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>122566.52476255927</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>4.35</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>2238.7211385683377</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
-        <x:v>122566.52476255927</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Large bathypelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>0.1073306876</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>4.34</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>2187.761623949552</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>0.1073306876</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>2187.761623949552</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$G$2:$G$230,A4,'Species'!$U$2:$U$230))</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>234.81395940339803</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>4.34</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>2187.761623949552</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
-        <x:v>234.81395940339803</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Large benthopelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>36480.6561857245</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>2.859419725588152</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>72.34686649391924</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>36480.6561857245</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>596.9317758172526</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$G$2:$G$230,A5,'Species'!$U$2:$U$230))</x:f>
-        <x:v>21776462.87992317</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>2.859419725588152</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>72.34686649391924</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>2639261.1626791796</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>19137201.717243988</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>8.250969319692993</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>7.2509693196929925</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Large demersals (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>81844.3867182691</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>4.359399520765832</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>2287.702362978008</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>81844.3867182691</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>2407.912263085692</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$G$2:$G$230,A6,'Species'!$U$2:$U$230))</x:f>
-        <x:v>197074102.4436479</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>4.359399520765832</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>2287.702362978008</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>187235596.8918701</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>9838505.55177778</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>1.0525461275264851</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>0.05254612752648519</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Large pelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>86205.07627928052</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>4.352883165952026</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>2253.6328575239227</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>86205.07627928052</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>2465.9476308876624</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$G$2:$G$230,A7,'Species'!$U$2:$U$230))</x:f>
-        <x:v>212577203.62138203</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>4.352883165952026</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>2253.6328575239227</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>194274592.38834268</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>18302611.23303935</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>1.0942100096983016</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>0.09421000969830158</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="18" customHeight="1">
       <x:c r="A8" s="24" t="str">
         <x:v>Large rays (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B8" s="33" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="D8" s="31" t="n">
+      <x:c r="B8" s="31" t="n">
         <x:v>5369.9829323123</x:v>
       </x:c>
+      <x:c r="C8" s="32" t="n">
+        <x:v>3.8118264612279464</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="n">
+        <x:f>IF(C8="","",(1/'Metadata'!$B$5)^(C8-1))</x:f>
+        <x:v>648.3752989256503</x:v>
+      </x:c>
       <x:c r="E8" s="31" t="n">
-        <x:v>5369.9829323123</x:v>
-      </x:c>
-      <x:c r="F8" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H8" s="32" t="n">
-        <x:f>IF(E8=0,"",I8/E8)</x:f>
-        <x:v>786.6802694941682</x:v>
-      </x:c>
-      <x:c r="I8" s="31" t="n">
-        <x:f>IF(C8=0,"",SUMIF('Species'!$G$2:$G$230,A8,'Species'!$U$2:$U$230))</x:f>
-        <x:v>4224459.620370524</x:v>
-      </x:c>
-      <x:c r="J8" s="32" t="n">
-        <x:v>3.8118264612279464</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
-        <x:f>IF(J8="","",(1/'Metadata'!$B$5)^(J8-1))</x:f>
-        <x:v>648.3752989256503</x:v>
-      </x:c>
-      <x:c r="L8" s="31" t="n">
-        <x:f>IF(E8=0,"",E8*K8)</x:f>
+        <x:f>IF(B8=0,"",B8*D8)</x:f>
         <x:v>3481764.288963628</x:v>
-      </x:c>
-      <x:c r="M8" s="31" t="n">
-        <x:f>IF(E8=0,"",I8-L8)</x:f>
-        <x:v>742695.331406896</x:v>
-      </x:c>
-      <x:c r="N8" s="32" t="n">
-        <x:f>IF(L8=0,"",I8/L8)</x:f>
-        <x:v>1.2133100548365854</x:v>
-      </x:c>
-      <x:c r="O8" s="34" t="n">
-        <x:f>IF(L8=0,"",M8/L8)</x:f>
-        <x:v>0.21331005483658533</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="18" customHeight="1">
       <x:c r="A9" s="24" t="str">
         <x:v>Large reef assoc. fish (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B9" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C9" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="D9" s="31" t="n">
+      <x:c r="B9" s="31" t="n">
         <x:v>3221.7991353274997</x:v>
       </x:c>
+      <x:c r="C9" s="32" t="n">
+        <x:v>4.132437664384073</x:v>
+      </x:c>
+      <x:c r="D9" s="32" t="n">
+        <x:f>IF(C9="","",(1/'Metadata'!$B$5)^(C9-1))</x:f>
+        <x:v>1356.5558057196367</x:v>
+      </x:c>
       <x:c r="E9" s="31" t="n">
-        <x:v>3221.7991353274997</x:v>
-      </x:c>
-      <x:c r="F9" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H9" s="32" t="n">
-        <x:f>IF(E9=0,"",I9/E9)</x:f>
-        <x:v>1661.879581484286</x:v>
-      </x:c>
-      <x:c r="I9" s="31" t="n">
-        <x:f>IF(C9=0,"",SUMIF('Species'!$G$2:$G$230,A9,'Species'!$U$2:$U$230))</x:f>
-        <x:v>5354242.1986445</x:v>
-      </x:c>
-      <x:c r="J9" s="32" t="n">
-        <x:v>4.132437664384073</x:v>
-      </x:c>
-      <x:c r="K9" s="32" t="n">
-        <x:f>IF(J9="","",(1/'Metadata'!$B$5)^(J9-1))</x:f>
-        <x:v>1356.5558057196367</x:v>
-      </x:c>
-      <x:c r="L9" s="31" t="n">
-        <x:f>IF(E9=0,"",E9*K9)</x:f>
+        <x:f>IF(B9=0,"",B9*D9)</x:f>
         <x:v>4370550.321891026</x:v>
-      </x:c>
-      <x:c r="M9" s="31" t="n">
-        <x:f>IF(E9=0,"",I9-L9)</x:f>
-        <x:v>983691.8767534746</x:v>
-      </x:c>
-      <x:c r="N9" s="32" t="n">
-        <x:f>IF(L9=0,"",I9/L9)</x:f>
-        <x:v>1.2250727721464276</x:v>
-      </x:c>
-      <x:c r="O9" s="34" t="n">
-        <x:f>IF(L9=0,"",M9/L9)</x:f>
-        <x:v>0.2250727721464276</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="18" customHeight="1">
       <x:c r="A10" s="24" t="str">
         <x:v>Large sharks (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B10" s="33" t="n">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="C10" s="33" t="n">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="D10" s="31" t="n">
+      <x:c r="B10" s="31" t="n">
         <x:v>9141.6133490033</x:v>
       </x:c>
+      <x:c r="C10" s="32" t="n">
+        <x:v>4.222972809588317</x:v>
+      </x:c>
+      <x:c r="D10" s="32" t="n">
+        <x:f>IF(C10="","",(1/'Metadata'!$B$5)^(C10-1))</x:f>
+        <x:v>1670.985993549218</x:v>
+      </x:c>
       <x:c r="E10" s="31" t="n">
-        <x:v>9141.6133490033</x:v>
-      </x:c>
-      <x:c r="F10" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G10" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H10" s="32" t="n">
-        <x:f>IF(E10=0,"",I10/E10)</x:f>
-        <x:v>2494.182120558098</x:v>
-      </x:c>
-      <x:c r="I10" s="31" t="n">
-        <x:f>IF(C10=0,"",SUMIF('Species'!$G$2:$G$230,A10,'Species'!$U$2:$U$230))</x:f>
-        <x:v>22800848.56813927</x:v>
-      </x:c>
-      <x:c r="J10" s="32" t="n">
-        <x:v>4.222972809588317</x:v>
-      </x:c>
-      <x:c r="K10" s="32" t="n">
-        <x:f>IF(J10="","",(1/'Metadata'!$B$5)^(J10-1))</x:f>
-        <x:v>1670.985993549218</x:v>
-      </x:c>
-      <x:c r="L10" s="31" t="n">
-        <x:f>IF(E10=0,"",E10*K10)</x:f>
+        <x:f>IF(B10=0,"",B10*D10)</x:f>
         <x:v>15275507.864627074</x:v>
-      </x:c>
-      <x:c r="M10" s="31" t="n">
-        <x:f>IF(E10=0,"",I10-L10)</x:f>
-        <x:v>7525340.7035121955</x:v>
-      </x:c>
-      <x:c r="N10" s="32" t="n">
-        <x:f>IF(L10=0,"",I10/L10)</x:f>
-        <x:v>1.4926409498265094</x:v>
-      </x:c>
-      <x:c r="O10" s="34" t="n">
-        <x:f>IF(L10=0,"",M10/L10)</x:f>
-        <x:v>0.49264094982650936</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="18" customHeight="1">
       <x:c r="A11" s="24" t="str">
         <x:v>Lobsters, crabs</x:v>
       </x:c>
-      <x:c r="B11" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C11" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D11" s="31" t="n">
+      <x:c r="B11" s="31" t="n">
         <x:v>765.7359944571999</x:v>
       </x:c>
+      <x:c r="C11" s="32" t="n">
+        <x:v>2.828205978587524</x:v>
+      </x:c>
+      <x:c r="D11" s="32" t="n">
+        <x:f>IF(C11="","",(1/'Metadata'!$B$5)^(C11-1))</x:f>
+        <x:v>67.32959135264758</x:v>
+      </x:c>
       <x:c r="E11" s="31" t="n">
-        <x:v>765.7359944571999</x:v>
-      </x:c>
-      <x:c r="F11" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G11" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H11" s="32" t="n">
-        <x:f>IF(E11=0,"",I11/E11)</x:f>
-        <x:v>101.81390624804413</x:v>
-      </x:c>
-      <x:c r="I11" s="31" t="n">
-        <x:f>IF(C11=0,"",SUMIF('Species'!$G$2:$G$230,A11,'Species'!$U$2:$U$230))</x:f>
-        <x:v>77962.5727504182</x:v>
-      </x:c>
-      <x:c r="J11" s="32" t="n">
-        <x:v>2.828205978587524</x:v>
-      </x:c>
-      <x:c r="K11" s="32" t="n">
-        <x:f>IF(J11="","",(1/'Metadata'!$B$5)^(J11-1))</x:f>
-        <x:v>67.32959135264758</x:v>
-      </x:c>
-      <x:c r="L11" s="31" t="n">
-        <x:f>IF(E11=0,"",E11*K11)</x:f>
+        <x:f>IF(B11=0,"",B11*D11)</x:f>
         <x:v>51556.69159081649</x:v>
-      </x:c>
-      <x:c r="M11" s="31" t="n">
-        <x:f>IF(E11=0,"",I11-L11)</x:f>
-        <x:v>26405.88115960171</x:v>
-      </x:c>
-      <x:c r="N11" s="32" t="n">
-        <x:f>IF(L11=0,"",I11/L11)</x:f>
-        <x:v>1.5121717539436772</x:v>
-      </x:c>
-      <x:c r="O11" s="34" t="n">
-        <x:f>IF(L11=0,"",M11/L11)</x:f>
-        <x:v>0.5121717539436772</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="18" customHeight="1">
       <x:c r="A12" s="24" t="str">
         <x:v>Medium bathydemersals (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B12" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C12" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D12" s="31" t="n">
+      <x:c r="B12" s="31" t="n">
         <x:v>6014.7413932566005</x:v>
       </x:c>
+      <x:c r="C12" s="32" t="n">
+        <x:v>4.499694345606891</x:v>
+      </x:c>
+      <x:c r="D12" s="32" t="n">
+        <x:f>IF(C12="","",(1/'Metadata'!$B$5)^(C12-1))</x:f>
+        <x:v>3160.0528471728076</x:v>
+      </x:c>
       <x:c r="E12" s="31" t="n">
-        <x:v>6014.7413932566005</x:v>
-      </x:c>
-      <x:c r="F12" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G12" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H12" s="32" t="n">
-        <x:f>IF(E12=0,"",I12/E12)</x:f>
-        <x:v>3160.1514811617412</x:v>
-      </x:c>
-      <x:c r="I12" s="31" t="n">
-        <x:f>IF(C12=0,"",SUMIF('Species'!$G$2:$G$230,A12,'Species'!$U$2:$U$230))</x:f>
-        <x:v>19007493.92270468</x:v>
-      </x:c>
-      <x:c r="J12" s="32" t="n">
-        <x:v>4.499694345606891</x:v>
-      </x:c>
-      <x:c r="K12" s="32" t="n">
-        <x:f>IF(J12="","",(1/'Metadata'!$B$5)^(J12-1))</x:f>
-        <x:v>3160.0528471728076</x:v>
-      </x:c>
-      <x:c r="L12" s="31" t="n">
-        <x:f>IF(E12=0,"",E12*K12)</x:f>
+        <x:f>IF(B12=0,"",B12*D12)</x:f>
         <x:v>19006900.66476866</x:v>
-      </x:c>
-      <x:c r="M12" s="31" t="n">
-        <x:f>IF(E12=0,"",I12-L12)</x:f>
-        <x:v>593.2579360231757</x:v>
-      </x:c>
-      <x:c r="N12" s="32" t="n">
-        <x:f>IF(L12=0,"",I12/L12)</x:f>
-        <x:v>1.0000312127656417</x:v>
-      </x:c>
-      <x:c r="O12" s="34" t="n">
-        <x:f>IF(L12=0,"",M12/L12)</x:f>
-        <x:v>0.00003121276564163053</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="18" customHeight="1">
       <x:c r="A13" s="24" t="str">
         <x:v>Medium bathypelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B13" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C13" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D13" s="31" t="n">
+      <x:c r="B13" s="31" t="n">
         <x:v>0.000325436</x:v>
       </x:c>
+      <x:c r="C13" s="32" t="n">
+        <x:v>4.08</x:v>
+      </x:c>
+      <x:c r="D13" s="32" t="n">
+        <x:f>IF(C13="","",(1/'Metadata'!$B$5)^(C13-1))</x:f>
+        <x:v>1202.2644346174131</x:v>
+      </x:c>
       <x:c r="E13" s="31" t="n">
-        <x:v>0.000325436</x:v>
-      </x:c>
-      <x:c r="F13" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G13" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H13" s="32" t="n">
-        <x:f>IF(E13=0,"",I13/E13)</x:f>
-        <x:v>1202.2644346174131</x:v>
-      </x:c>
-      <x:c r="I13" s="31" t="n">
-        <x:f>IF(C13=0,"",SUMIF('Species'!$G$2:$G$230,A13,'Species'!$U$2:$U$230))</x:f>
+        <x:f>IF(B13=0,"",B13*D13)</x:f>
         <x:v>0.3912601285441525</x:v>
-      </x:c>
-      <x:c r="J13" s="32" t="n">
-        <x:v>4.08</x:v>
-      </x:c>
-      <x:c r="K13" s="32" t="n">
-        <x:f>IF(J13="","",(1/'Metadata'!$B$5)^(J13-1))</x:f>
-        <x:v>1202.2644346174131</x:v>
-      </x:c>
-      <x:c r="L13" s="31" t="n">
-        <x:f>IF(E13=0,"",E13*K13)</x:f>
-        <x:v>0.3912601285441525</x:v>
-      </x:c>
-      <x:c r="M13" s="31" t="n">
-        <x:f>IF(E13=0,"",I13-L13)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N13" s="32" t="n">
-        <x:f>IF(L13=0,"",I13/L13)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O13" s="34" t="n">
-        <x:f>IF(L13=0,"",M13/L13)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="18" customHeight="1">
       <x:c r="A14" s="24" t="str">
         <x:v>Medium benthopelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B14" s="33" t="n">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="C14" s="33" t="n">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="D14" s="31" t="n">
+      <x:c r="B14" s="31" t="n">
         <x:v>59713.53366290111</x:v>
       </x:c>
+      <x:c r="C14" s="32" t="n">
+        <x:v>2.793862411764626</x:v>
+      </x:c>
+      <x:c r="D14" s="32" t="n">
+        <x:f>IF(C14="","",(1/'Metadata'!$B$5)^(C14-1))</x:f>
+        <x:v>62.210316630087576</x:v>
+      </x:c>
       <x:c r="E14" s="31" t="n">
-        <x:v>59713.53366290111</x:v>
-      </x:c>
-      <x:c r="F14" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G14" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H14" s="32" t="n">
-        <x:f>IF(E14=0,"",I14/E14)</x:f>
-        <x:v>240.72814981044547</x:v>
-      </x:c>
-      <x:c r="I14" s="31" t="n">
-        <x:f>IF(C14=0,"",SUMIF('Species'!$G$2:$G$230,A14,'Species'!$U$2:$U$230))</x:f>
-        <x:v>14374728.477313936</x:v>
-      </x:c>
-      <x:c r="J14" s="32" t="n">
-        <x:v>2.793862411764626</x:v>
-      </x:c>
-      <x:c r="K14" s="32" t="n">
-        <x:f>IF(J14="","",(1/'Metadata'!$B$5)^(J14-1))</x:f>
-        <x:v>62.210316630087576</x:v>
-      </x:c>
-      <x:c r="L14" s="31" t="n">
-        <x:f>IF(E14=0,"",E14*K14)</x:f>
+        <x:f>IF(B14=0,"",B14*D14)</x:f>
         <x:v>3714797.836270471</x:v>
-      </x:c>
-      <x:c r="M14" s="31" t="n">
-        <x:f>IF(E14=0,"",I14-L14)</x:f>
-        <x:v>10659930.641043466</x:v>
-      </x:c>
-      <x:c r="N14" s="32" t="n">
-        <x:f>IF(L14=0,"",I14/L14)</x:f>
-        <x:v>3.869585670843845</x:v>
-      </x:c>
-      <x:c r="O14" s="34" t="n">
-        <x:f>IF(L14=0,"",M14/L14)</x:f>
-        <x:v>2.8695856708438456</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="18" customHeight="1">
       <x:c r="A15" s="24" t="str">
         <x:v>Medium demersals (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B15" s="33" t="n">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="C15" s="33" t="n">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="D15" s="31" t="n">
+      <x:c r="B15" s="31" t="n">
         <x:v>190691.3477993141</x:v>
       </x:c>
+      <x:c r="C15" s="32" t="n">
+        <x:v>3.28622162700191</x:v>
+      </x:c>
+      <x:c r="D15" s="32" t="n">
+        <x:f>IF(C15="","",(1/'Metadata'!$B$5)^(C15-1))</x:f>
+        <x:v>193.2954481093906</x:v>
+      </x:c>
       <x:c r="E15" s="31" t="n">
-        <x:v>190691.3477993141</x:v>
-      </x:c>
-      <x:c r="F15" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G15" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H15" s="32" t="n">
-        <x:f>IF(E15=0,"",I15/E15)</x:f>
-        <x:v>201.4956885391603</x:v>
-      </x:c>
-      <x:c r="I15" s="31" t="n">
-        <x:f>IF(C15=0,"",SUMIF('Species'!$G$2:$G$230,A15,'Species'!$U$2:$U$230))</x:f>
-        <x:v>38423484.42328329</x:v>
-      </x:c>
-      <x:c r="J15" s="32" t="n">
-        <x:v>3.28622162700191</x:v>
-      </x:c>
-      <x:c r="K15" s="32" t="n">
-        <x:f>IF(J15="","",(1/'Metadata'!$B$5)^(J15-1))</x:f>
-        <x:v>193.2954481093906</x:v>
-      </x:c>
-      <x:c r="L15" s="31" t="n">
-        <x:f>IF(E15=0,"",E15*K15)</x:f>
+        <x:f>IF(B15=0,"",B15*D15)</x:f>
         <x:v>36859769.52345207</x:v>
-      </x:c>
-      <x:c r="M15" s="31" t="n">
-        <x:f>IF(E15=0,"",I15-L15)</x:f>
-        <x:v>1563714.899831213</x:v>
-      </x:c>
-      <x:c r="N15" s="32" t="n">
-        <x:f>IF(L15=0,"",I15/L15)</x:f>
-        <x:v>1.0424233499028337</x:v>
-      </x:c>
-      <x:c r="O15" s="34" t="n">
-        <x:f>IF(L15=0,"",M15/L15)</x:f>
-        <x:v>0.042423349902833696</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="18" customHeight="1">
       <x:c r="A16" s="24" t="str">
         <x:v>Medium pelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B16" s="33" t="n">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="C16" s="33" t="n">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="D16" s="31" t="n">
+      <x:c r="B16" s="31" t="n">
         <x:v>716884.8831005016</x:v>
       </x:c>
+      <x:c r="C16" s="32" t="n">
+        <x:v>3.6147078837098117</x:v>
+      </x:c>
+      <x:c r="D16" s="32" t="n">
+        <x:f>IF(C16="","",(1/'Metadata'!$B$5)^(C16-1))</x:f>
+        <x:v>411.82042618624024</x:v>
+      </x:c>
       <x:c r="E16" s="31" t="n">
-        <x:v>716884.8831005016</x:v>
-      </x:c>
-      <x:c r="F16" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G16" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H16" s="32" t="n">
-        <x:f>IF(E16=0,"",I16/E16)</x:f>
-        <x:v>493.0492332533638</x:v>
-      </x:c>
-      <x:c r="I16" s="31" t="n">
-        <x:f>IF(C16=0,"",SUMIF('Species'!$G$2:$G$230,A16,'Species'!$U$2:$U$230))</x:f>
-        <x:v>353459541.9436297</x:v>
-      </x:c>
-      <x:c r="J16" s="32" t="n">
-        <x:v>3.6147078837098117</x:v>
-      </x:c>
-      <x:c r="K16" s="32" t="n">
-        <x:f>IF(J16="","",(1/'Metadata'!$B$5)^(J16-1))</x:f>
-        <x:v>411.82042618624024</x:v>
-      </x:c>
-      <x:c r="L16" s="31" t="n">
-        <x:f>IF(E16=0,"",E16*K16)</x:f>
+        <x:f>IF(B16=0,"",B16*D16)</x:f>
         <x:v>295227838.0849216</x:v>
-      </x:c>
-      <x:c r="M16" s="31" t="n">
-        <x:f>IF(E16=0,"",I16-L16)</x:f>
-        <x:v>58231703.85870808</x:v>
-      </x:c>
-      <x:c r="N16" s="32" t="n">
-        <x:f>IF(L16=0,"",I16/L16)</x:f>
-        <x:v>1.1972432689154398</x:v>
-      </x:c>
-      <x:c r="O16" s="34" t="n">
-        <x:f>IF(L16=0,"",M16/L16)</x:f>
-        <x:v>0.1972432689154397</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="18" customHeight="1">
       <x:c r="A17" s="24" t="str">
         <x:v>Medium reef assoc. fish (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B17" s="33" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="C17" s="33" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="D17" s="31" t="n">
+      <x:c r="B17" s="31" t="n">
         <x:v>9079.408478495</x:v>
       </x:c>
+      <x:c r="C17" s="32" t="n">
+        <x:v>2.946107201569475</x:v>
+      </x:c>
+      <x:c r="D17" s="32" t="n">
+        <x:f>IF(C17="","",(1/'Metadata'!$B$5)^(C17-1))</x:f>
+        <x:v>88.32979074163656</x:v>
+      </x:c>
       <x:c r="E17" s="31" t="n">
-        <x:v>9079.408478495</x:v>
-      </x:c>
-      <x:c r="F17" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G17" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H17" s="32" t="n">
-        <x:f>IF(E17=0,"",I17/E17)</x:f>
-        <x:v>208.66762438395125</x:v>
-      </x:c>
-      <x:c r="I17" s="31" t="n">
-        <x:f>IF(C17=0,"",SUMIF('Species'!$G$2:$G$230,A17,'Species'!$U$2:$U$230))</x:f>
-        <x:v>1894578.5980190567</x:v>
-      </x:c>
-      <x:c r="J17" s="32" t="n">
-        <x:v>2.946107201569475</x:v>
-      </x:c>
-      <x:c r="K17" s="32" t="n">
-        <x:f>IF(J17="","",(1/'Metadata'!$B$5)^(J17-1))</x:f>
-        <x:v>88.32979074163656</x:v>
-      </x:c>
-      <x:c r="L17" s="31" t="n">
-        <x:f>IF(E17=0,"",E17*K17)</x:f>
+        <x:f>IF(B17=0,"",B17*D17)</x:f>
         <x:v>801982.2509633041</x:v>
-      </x:c>
-      <x:c r="M17" s="31" t="n">
-        <x:f>IF(E17=0,"",I17-L17)</x:f>
-        <x:v>1092596.3470557528</x:v>
-      </x:c>
-      <x:c r="N17" s="32" t="n">
-        <x:f>IF(L17=0,"",I17/L17)</x:f>
-        <x:v>2.3623697354191773</x:v>
-      </x:c>
-      <x:c r="O17" s="34" t="n">
-        <x:f>IF(L17=0,"",M17/L17)</x:f>
-        <x:v>1.3623697354191773</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="18" customHeight="1">
       <x:c r="A18" s="24" t="str">
         <x:v>Other demersal invertebrates</x:v>
       </x:c>
-      <x:c r="B18" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C18" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="D18" s="31" t="n">
+      <x:c r="B18" s="31" t="n">
         <x:v>7539.9465079549</x:v>
       </x:c>
+      <x:c r="C18" s="32" t="n">
+        <x:v>2.0141011499888632</x:v>
+      </x:c>
+      <x:c r="D18" s="32" t="n">
+        <x:f>IF(C18="","",(1/'Metadata'!$B$5)^(C18-1))</x:f>
+        <x:v>10.330019705742984</x:v>
+      </x:c>
       <x:c r="E18" s="31" t="n">
-        <x:v>7539.9465079549</x:v>
-      </x:c>
-      <x:c r="F18" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G18" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H18" s="32" t="n">
-        <x:f>IF(E18=0,"",I18/E18)</x:f>
-        <x:v>10.697469124151723</x:v>
-      </x:c>
-      <x:c r="I18" s="31" t="n">
-        <x:f>IF(C18=0,"",SUMIF('Species'!$G$2:$G$230,A18,'Species'!$U$2:$U$230))</x:f>
-        <x:v>80658.34496660315</x:v>
-      </x:c>
-      <x:c r="J18" s="32" t="n">
-        <x:v>2.0141011499888632</x:v>
-      </x:c>
-      <x:c r="K18" s="32" t="n">
-        <x:f>IF(J18="","",(1/'Metadata'!$B$5)^(J18-1))</x:f>
-        <x:v>10.330019705742984</x:v>
-      </x:c>
-      <x:c r="L18" s="31" t="n">
-        <x:f>IF(E18=0,"",E18*K18)</x:f>
+        <x:f>IF(B18=0,"",B18*D18)</x:f>
         <x:v>77887.79600742212</x:v>
-      </x:c>
-      <x:c r="M18" s="31" t="n">
-        <x:f>IF(E18=0,"",I18-L18)</x:f>
-        <x:v>2770.548959181033</x:v>
-      </x:c>
-      <x:c r="N18" s="32" t="n">
-        <x:f>IF(L18=0,"",I18/L18)</x:f>
-        <x:v>1.0355710278272223</x:v>
-      </x:c>
-      <x:c r="O18" s="34" t="n">
-        <x:f>IF(L18=0,"",M18/L18)</x:f>
-        <x:v>0.035571027827222386</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="18" customHeight="1">
       <x:c r="A19" s="24" t="str">
         <x:v>Shrimps</x:v>
       </x:c>
-      <x:c r="B19" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C19" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="D19" s="31" t="n">
+      <x:c r="B19" s="31" t="n">
         <x:v>6502.1485245754</x:v>
       </x:c>
+      <x:c r="C19" s="32" t="n">
+        <x:v>3.114652103387514</x:v>
+      </x:c>
+      <x:c r="D19" s="32" t="n">
+        <x:f>IF(C19="","",(1/'Metadata'!$B$5)^(C19-1))</x:f>
+        <x:v>130.2123279657059</x:v>
+      </x:c>
       <x:c r="E19" s="31" t="n">
-        <x:v>6502.1485245754</x:v>
-      </x:c>
-      <x:c r="F19" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G19" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H19" s="32" t="n">
-        <x:f>IF(E19=0,"",I19/E19)</x:f>
-        <x:v>153.61719597785103</x:v>
-      </x:c>
-      <x:c r="I19" s="31" t="n">
-        <x:f>IF(C19=0,"",SUMIF('Species'!$G$2:$G$230,A19,'Species'!$U$2:$U$230))</x:f>
-        <x:v>998841.8241767942</x:v>
-      </x:c>
-      <x:c r="J19" s="32" t="n">
-        <x:v>3.114652103387514</x:v>
-      </x:c>
-      <x:c r="K19" s="32" t="n">
-        <x:f>IF(J19="","",(1/'Metadata'!$B$5)^(J19-1))</x:f>
-        <x:v>130.2123279657059</x:v>
-      </x:c>
-      <x:c r="L19" s="31" t="n">
-        <x:f>IF(E19=0,"",E19*K19)</x:f>
+        <x:f>IF(B19=0,"",B19*D19)</x:f>
         <x:v>846659.8961637428</x:v>
-      </x:c>
-      <x:c r="M19" s="31" t="n">
-        <x:f>IF(E19=0,"",I19-L19)</x:f>
-        <x:v>152181.9280130514</x:v>
-      </x:c>
-      <x:c r="N19" s="32" t="n">
-        <x:f>IF(L19=0,"",I19/L19)</x:f>
-        <x:v>1.1797438720111761</x:v>
-      </x:c>
-      <x:c r="O19" s="34" t="n">
-        <x:f>IF(L19=0,"",M19/L19)</x:f>
-        <x:v>0.17974387201117606</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="18" customHeight="1">
       <x:c r="A20" s="24" t="str">
         <x:v>Small benthopelagics (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B20" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C20" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D20" s="31" t="n">
+      <x:c r="B20" s="31" t="n">
         <x:v>2191.9774130155997</x:v>
       </x:c>
+      <x:c r="C20" s="32" t="n">
+        <x:v>3.19</x:v>
+      </x:c>
+      <x:c r="D20" s="32" t="n">
+        <x:f>IF(C20="","",(1/'Metadata'!$B$5)^(C20-1))</x:f>
+        <x:v>154.88166189124811</x:v>
+      </x:c>
       <x:c r="E20" s="31" t="n">
-        <x:v>2191.9774130155997</x:v>
-      </x:c>
-      <x:c r="F20" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G20" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H20" s="32" t="n">
-        <x:f>IF(E20=0,"",I20/E20)</x:f>
-        <x:v>154.88166189124811</x:v>
-      </x:c>
-      <x:c r="I20" s="31" t="n">
-        <x:f>IF(C20=0,"",SUMIF('Species'!$G$2:$G$230,A20,'Species'!$U$2:$U$230))</x:f>
+        <x:f>IF(B20=0,"",B20*D20)</x:f>
         <x:v>339497.10455593484</x:v>
-      </x:c>
-      <x:c r="J20" s="32" t="n">
-        <x:v>3.19</x:v>
-      </x:c>
-      <x:c r="K20" s="32" t="n">
-        <x:f>IF(J20="","",(1/'Metadata'!$B$5)^(J20-1))</x:f>
-        <x:v>154.88166189124811</x:v>
-      </x:c>
-      <x:c r="L20" s="31" t="n">
-        <x:f>IF(E20=0,"",E20*K20)</x:f>
-        <x:v>339497.10455593484</x:v>
-      </x:c>
-      <x:c r="M20" s="31" t="n">
-        <x:f>IF(E20=0,"",I20-L20)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N20" s="32" t="n">
-        <x:f>IF(L20=0,"",I20/L20)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O20" s="34" t="n">
-        <x:f>IF(L20=0,"",M20/L20)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="18" customHeight="1">
       <x:c r="A21" s="24" t="str">
         <x:v>Small demersals (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B21" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C21" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D21" s="31" t="n">
+      <x:c r="B21" s="31" t="n">
         <x:v>6591.1289582198</x:v>
       </x:c>
+      <x:c r="C21" s="32" t="n">
+        <x:v>3.0815767679852573</x:v>
+      </x:c>
+      <x:c r="D21" s="32" t="n">
+        <x:f>IF(C21="","",(1/'Metadata'!$B$5)^(C21-1))</x:f>
+        <x:v>120.66373603809065</x:v>
+      </x:c>
       <x:c r="E21" s="31" t="n">
-        <x:v>6591.1289582198</x:v>
-      </x:c>
-      <x:c r="F21" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G21" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H21" s="32" t="n">
-        <x:f>IF(E21=0,"",I21/E21)</x:f>
-        <x:v>234.31041820140035</x:v>
-      </x:c>
-      <x:c r="I21" s="31" t="n">
-        <x:f>IF(C21=0,"",SUMIF('Species'!$G$2:$G$230,A21,'Species'!$U$2:$U$230))</x:f>
-        <x:v>1544370.1826198415</x:v>
-      </x:c>
-      <x:c r="J21" s="32" t="n">
-        <x:v>3.0815767679852573</x:v>
-      </x:c>
-      <x:c r="K21" s="32" t="n">
-        <x:f>IF(J21="","",(1/'Metadata'!$B$5)^(J21-1))</x:f>
-        <x:v>120.66373603809065</x:v>
-      </x:c>
-      <x:c r="L21" s="31" t="n">
-        <x:f>IF(E21=0,"",E21*K21)</x:f>
+        <x:f>IF(B21=0,"",B21*D21)</x:f>
         <x:v>795310.2448076493</x:v>
-      </x:c>
-      <x:c r="M21" s="31" t="n">
-        <x:f>IF(E21=0,"",I21-L21)</x:f>
-        <x:v>749059.9378121922</x:v>
-      </x:c>
-      <x:c r="N21" s="32" t="n">
-        <x:f>IF(L21=0,"",I21/L21)</x:f>
-        <x:v>1.9418462074424265</x:v>
-      </x:c>
-      <x:c r="O21" s="34" t="n">
-        <x:f>IF(L21=0,"",M21/L21)</x:f>
-        <x:v>0.9418462074424265</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="18" customHeight="1">
       <x:c r="A22" s="24" t="str">
         <x:v>Small pelagics (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B22" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C22" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="D22" s="31" t="n">
+      <x:c r="B22" s="31" t="n">
         <x:v>924413.6595826818</x:v>
       </x:c>
+      <x:c r="C22" s="32" t="n">
+        <x:v>2.995630975665107</x:v>
+      </x:c>
+      <x:c r="D22" s="32" t="n">
+        <x:f>IF(C22="","",(1/'Metadata'!$B$5)^(C22-1))</x:f>
+        <x:v>98.99903827402717</x:v>
+      </x:c>
       <x:c r="E22" s="31" t="n">
-        <x:v>924413.6595826818</x:v>
-      </x:c>
-      <x:c r="F22" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G22" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H22" s="32" t="n">
-        <x:f>IF(E22=0,"",I22/E22)</x:f>
-        <x:v>113.60321264375847</x:v>
-      </x:c>
-      <x:c r="I22" s="31" t="n">
-        <x:f>IF(C22=0,"",SUMIF('Species'!$G$2:$G$230,A22,'Species'!$U$2:$U$230))</x:f>
-        <x:v>105016361.54036635</x:v>
-      </x:c>
-      <x:c r="J22" s="32" t="n">
-        <x:v>2.995630975665107</x:v>
-      </x:c>
-      <x:c r="K22" s="32" t="n">
-        <x:f>IF(J22="","",(1/'Metadata'!$B$5)^(J22-1))</x:f>
-        <x:v>98.99903827402717</x:v>
-      </x:c>
-      <x:c r="L22" s="31" t="n">
-        <x:f>IF(E22=0,"",E22*K22)</x:f>
+        <x:f>IF(B22=0,"",B22*D22)</x:f>
         <x:v>91516063.26605944</x:v>
-      </x:c>
-      <x:c r="M22" s="31" t="n">
-        <x:f>IF(E22=0,"",I22-L22)</x:f>
-        <x:v>13500298.274306908</x:v>
-      </x:c>
-      <x:c r="N22" s="32" t="n">
-        <x:f>IF(L22=0,"",I22/L22)</x:f>
-        <x:v>1.1475183458783433</x:v>
-      </x:c>
-      <x:c r="O22" s="34" t="n">
-        <x:f>IF(L22=0,"",M22/L22)</x:f>
-        <x:v>0.14751834587834334</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="18" customHeight="1">
       <x:c r="A23" s="24" t="str">
         <x:v>Small reef assoc. fish (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B23" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C23" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D23" s="31" t="n">
+      <x:c r="B23" s="31" t="n">
         <x:v>518.2224500254999</x:v>
       </x:c>
+      <x:c r="C23" s="32" t="n">
+        <x:v>2.03</x:v>
+      </x:c>
+      <x:c r="D23" s="32" t="n">
+        <x:f>IF(C23="","",(1/'Metadata'!$B$5)^(C23-1))</x:f>
+        <x:v>10.71519305237606</x:v>
+      </x:c>
       <x:c r="E23" s="31" t="n">
-        <x:v>518.2224500254999</x:v>
-      </x:c>
-      <x:c r="F23" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G23" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H23" s="32" t="n">
-        <x:f>IF(E23=0,"",I23/E23)</x:f>
-        <x:v>10.71519305237606</x:v>
-      </x:c>
-      <x:c r="I23" s="31" t="n">
-        <x:f>IF(C23=0,"",SUMIF('Species'!$G$2:$G$230,A23,'Species'!$U$2:$U$230))</x:f>
+        <x:f>IF(B23=0,"",B23*D23)</x:f>
         <x:v>5552.853596098537</x:v>
-      </x:c>
-      <x:c r="J23" s="32" t="n">
-        <x:v>2.03</x:v>
-      </x:c>
-      <x:c r="K23" s="32" t="n">
-        <x:f>IF(J23="","",(1/'Metadata'!$B$5)^(J23-1))</x:f>
-        <x:v>10.71519305237606</x:v>
-      </x:c>
-      <x:c r="L23" s="31" t="n">
-        <x:f>IF(E23=0,"",E23*K23)</x:f>
-        <x:v>5552.853596098537</x:v>
-      </x:c>
-      <x:c r="M23" s="31" t="n">
-        <x:f>IF(E23=0,"",I23-L23)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N23" s="32" t="n">
-        <x:f>IF(L23=0,"",I23/L23)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O23" s="34" t="n">
-        <x:f>IF(L23=0,"",M23/L23)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="18" customHeight="1">
       <x:c r="A24" s="24" t="str">
         <x:v>Small to medium flatfishes (&lt;90 cm)</x:v>
       </x:c>
-      <x:c r="B24" s="33" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="C24" s="33" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="D24" s="31" t="n">
+      <x:c r="B24" s="31" t="n">
         <x:v>3643.2691632292003</x:v>
       </x:c>
+      <x:c r="C24" s="32" t="n">
+        <x:v>3.3428829878654733</x:v>
+      </x:c>
+      <x:c r="D24" s="32" t="n">
+        <x:f>IF(C24="","",(1/'Metadata'!$B$5)^(C24-1))</x:f>
+        <x:v>220.23330076537536</x:v>
+      </x:c>
       <x:c r="E24" s="31" t="n">
-        <x:v>3643.2691632292003</x:v>
-      </x:c>
-      <x:c r="F24" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G24" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H24" s="32" t="n">
-        <x:f>IF(E24=0,"",I24/E24)</x:f>
-        <x:v>328.03709275865907</x:v>
-      </x:c>
-      <x:c r="I24" s="31" t="n">
-        <x:f>IF(C24=0,"",SUMIF('Species'!$G$2:$G$230,A24,'Species'!$U$2:$U$230))</x:f>
-        <x:v>1195127.4244429795</x:v>
-      </x:c>
-      <x:c r="J24" s="32" t="n">
-        <x:v>3.3428829878654733</x:v>
-      </x:c>
-      <x:c r="K24" s="32" t="n">
-        <x:f>IF(J24="","",(1/'Metadata'!$B$5)^(J24-1))</x:f>
-        <x:v>220.23330076537536</x:v>
-      </x:c>
-      <x:c r="L24" s="31" t="n">
-        <x:f>IF(E24=0,"",E24*K24)</x:f>
+        <x:f>IF(B24=0,"",B24*D24)</x:f>
         <x:v>802369.1933946739</x:v>
-      </x:c>
-      <x:c r="M24" s="31" t="n">
-        <x:f>IF(E24=0,"",I24-L24)</x:f>
-        <x:v>392758.23104830564</x:v>
-      </x:c>
-      <x:c r="N24" s="32" t="n">
-        <x:f>IF(L24=0,"",I24/L24)</x:f>
-        <x:v>1.4894981440982538</x:v>
-      </x:c>
-      <x:c r="O24" s="34" t="n">
-        <x:f>IF(L24=0,"",M24/L24)</x:f>
-        <x:v>0.48949814409825365</x:v>
       </x:c>
     </x:row>
     <x:row r="25" ht="18" customHeight="1">
       <x:c r="A25" s="24" t="str">
         <x:v>Small to medium rays (&lt;90 cm)</x:v>
       </x:c>
-      <x:c r="B25" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C25" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D25" s="31" t="n">
+      <x:c r="B25" s="31" t="n">
         <x:v>722.6990892128999</x:v>
       </x:c>
+      <x:c r="C25" s="32" t="n">
+        <x:v>3.6619983998909076</x:v>
+      </x:c>
+      <x:c r="D25" s="32" t="n">
+        <x:f>IF(C25="","",(1/'Metadata'!$B$5)^(C25-1))</x:f>
+        <x:v>459.19632097663873</x:v>
+      </x:c>
       <x:c r="E25" s="31" t="n">
-        <x:v>722.6990892128999</x:v>
-      </x:c>
-      <x:c r="F25" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G25" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H25" s="32" t="n">
-        <x:f>IF(E25=0,"",I25/E25)</x:f>
-        <x:v>477.26658021933116</x:v>
-      </x:c>
-      <x:c r="I25" s="31" t="n">
-        <x:f>IF(C25=0,"",SUMIF('Species'!$G$2:$G$230,A25,'Species'!$U$2:$U$230))</x:f>
-        <x:v>344920.12283626606</x:v>
-      </x:c>
-      <x:c r="J25" s="32" t="n">
-        <x:v>3.6619983998909076</x:v>
-      </x:c>
-      <x:c r="K25" s="32" t="n">
-        <x:f>IF(J25="","",(1/'Metadata'!$B$5)^(J25-1))</x:f>
-        <x:v>459.19632097663873</x:v>
-      </x:c>
-      <x:c r="L25" s="31" t="n">
-        <x:f>IF(E25=0,"",E25*K25)</x:f>
+        <x:f>IF(B25=0,"",B25*D25)</x:f>
         <x:v>331860.76293973124</x:v>
-      </x:c>
-      <x:c r="M25" s="31" t="n">
-        <x:f>IF(E25=0,"",I25-L25)</x:f>
-        <x:v>13059.359896534821</x:v>
-      </x:c>
-      <x:c r="N25" s="32" t="n">
-        <x:f>IF(L25=0,"",I25/L25)</x:f>
-        <x:v>1.039351925129234</x:v>
-      </x:c>
-      <x:c r="O25" s="34" t="n">
-        <x:f>IF(L25=0,"",M25/L25)</x:f>
-        <x:v>0.03935192512923413</x:v>
       </x:c>
     </x:row>
     <x:row r="26" ht="18" customHeight="1">
       <x:c r="A26" s="24" t="str">
         <x:v>Small to medium sharks (&lt;90 cm)</x:v>
       </x:c>
-      <x:c r="B26" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C26" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D26" s="31" t="n">
+      <x:c r="B26" s="31" t="n">
         <x:v>16.0464861075</x:v>
       </x:c>
+      <x:c r="C26" s="32" t="n">
+        <x:v>3.79</x:v>
+      </x:c>
+      <x:c r="D26" s="32" t="n">
+        <x:f>IF(C26="","",(1/'Metadata'!$B$5)^(C26-1))</x:f>
+        <x:v>616.5950018614822</x:v>
+      </x:c>
       <x:c r="E26" s="31" t="n">
-        <x:v>16.0464861075</x:v>
-      </x:c>
-      <x:c r="F26" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G26" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H26" s="32" t="n">
-        <x:f>IF(E26=0,"",I26/E26)</x:f>
-        <x:v>616.5950018614822</x:v>
-      </x:c>
-      <x:c r="I26" s="31" t="n">
-        <x:f>IF(C26=0,"",SUMIF('Species'!$G$2:$G$230,A26,'Species'!$U$2:$U$230))</x:f>
+        <x:f>IF(B26=0,"",B26*D26)</x:f>
         <x:v>9894.183131324211</x:v>
       </x:c>
-      <x:c r="J26" s="32" t="n">
-        <x:v>3.79</x:v>
-      </x:c>
-      <x:c r="K26" s="32" t="n">
-        <x:f>IF(J26="","",(1/'Metadata'!$B$5)^(J26-1))</x:f>
-        <x:v>616.5950018614822</x:v>
-      </x:c>
-      <x:c r="L26" s="31" t="n">
-        <x:f>IF(E26=0,"",E26*K26)</x:f>
-        <x:v>9894.183131324211</x:v>
-      </x:c>
-      <x:c r="M26" s="31" t="n">
-        <x:f>IF(E26=0,"",I26-L26)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N26" s="32" t="n">
-        <x:f>IF(L26=0,"",I26/L26)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O26" s="34" t="n">
-        <x:f>IF(L26=0,"",M26/L26)</x:f>
-        <x:v>0</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G26">
-    <x:cfRule type="cellIs" dxfId="2" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O26">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rced405780a334497"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb5046a072f864d99"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -18336,7 +16922,7 @@
       <x:c r="B5" s="24" t="str">
         <x:v>catch_reconciled</x:v>
       </x:c>
-      <x:c r="C5" s="35" t="b">
+      <x:c r="C5" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D5" s="24" t="str">
@@ -18435,7 +17021,7 @@
         <x:v>commercial_ppr</x:v>
       </x:c>
       <x:c r="C12" s="24" t="n">
-        <x:v>1032601351.4376886</x:v>
+        <x:v>881884300.2249317</x:v>
       </x:c>
       <x:c r="D12" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -18449,7 +17035,7 @@
         <x:v>functional_ppr</x:v>
       </x:c>
       <x:c r="C13" s="24" t="n">
-        <x:v>1032601351.4376887</x:v>
+        <x:v>887683160.6813964</x:v>
       </x:c>
       <x:c r="D13" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -18463,7 +17049,7 @@
         <x:v>commercial_ppr_difference</x:v>
       </x:c>
       <x:c r="C14" s="24" t="n">
-        <x:v>-1.1920928955078125e-7</x:v>
+        <x:v>-150717051.212757</x:v>
       </x:c>
       <x:c r="D14" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -18477,7 +17063,7 @@
         <x:v>functional_ppr_difference</x:v>
       </x:c>
       <x:c r="C15" s="24" t="n">
-        <x:v>0</x:v>
+        <x:v>-144918190.75629234</x:v>
       </x:c>
       <x:c r="D15" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -18488,9 +17074,9 @@
         <x:v>EEZ_478</x:v>
       </x:c>
       <x:c r="B16" s="24" t="str">
-        <x:v>commercial_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C16" s="35" t="b">
+        <x:v>tl_coverage_complete</x:v>
+      </x:c>
+      <x:c r="C16" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D16" s="24" t="str">
@@ -18502,47 +17088,19 @@
         <x:v>EEZ_478</x:v>
       </x:c>
       <x:c r="B17" s="24" t="str">
-        <x:v>functional_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C17" s="35" t="b">
+        <x:v>group_ppr_within_convexity_bound</x:v>
+      </x:c>
+      <x:c r="C17" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D17" s="24" t="str">
         <x:v>boolean</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" ht="18" customHeight="1">
-      <x:c r="A18" s="24" t="str">
-        <x:v>EEZ_478</x:v>
-      </x:c>
-      <x:c r="B18" s="24" t="str">
-        <x:v>commercial_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C18" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D18" s="24" t="str">
-        <x:v>count</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" ht="18" customHeight="1">
-      <x:c r="A19" s="24" t="str">
-        <x:v>EEZ_478</x:v>
-      </x:c>
-      <x:c r="B19" s="24" t="str">
-        <x:v>functional_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C19" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D19" s="24" t="str">
-        <x:v>count</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc198feea0e474e4e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf67e0bff8476462f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -18589,7 +17147,7 @@
       <x:c r="A5" s="22" t="str">
         <x:v>Transfer efficiency</x:v>
       </x:c>
-      <x:c r="B5" s="36" t="n">
+      <x:c r="B5" s="34" t="n">
         <x:v>0.1</x:v>
       </x:c>
       <x:c r="C5" s="18" t="str">
